--- a/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_6_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_6_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.248478</v>
+        <v>0.243157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.522532</v>
+        <v>0.5381899999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.60799</v>
+        <v>0.571785</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5620309999999999</v>
+        <v>0.5544790000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.250792</v>
+        <v>0.252149</v>
       </c>
       <c r="K2" t="n">
-        <v>0.574219</v>
+        <v>0.571429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.65625</v>
+        <v>0.535714</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6125</v>
+        <v>0.552995</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_13.txt</t>
+          <t>_2_6_1_1790732533_19.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,42 +682,42 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.246438</v>
+        <v>0.248545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.551047</v>
+        <v>0.526667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.525593</v>
+        <v>0.59176</v>
       </c>
       <c r="I3" t="n">
-        <v>0.538019</v>
+        <v>0.557319</v>
       </c>
       <c r="J3" t="n">
-        <v>0.252281</v>
+        <v>0.251014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.567442</v>
+        <v>0.576613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.544643</v>
+        <v>0.638393</v>
       </c>
       <c r="M3" t="n">
-        <v>0.555809</v>
+        <v>0.605932</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,23 +753,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_13.txt</t>
+          <t>_2_3_3_1_1790732581_7.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>6</v>
       </c>
       <c r="AA3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -783,7 +783,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.248507</v>
+        <v>0.248567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5278080000000001</v>
+        <v>0.5223370000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.604245</v>
+        <v>0.569288</v>
       </c>
       <c r="I4" t="n">
-        <v>0.563446</v>
+        <v>0.544803</v>
       </c>
       <c r="J4" t="n">
-        <v>0.251064</v>
+        <v>0.250948</v>
       </c>
       <c r="K4" t="n">
-        <v>0.570281</v>
+        <v>0.57438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.633929</v>
+        <v>0.620536</v>
       </c>
       <c r="M4" t="n">
-        <v>0.600423</v>
+        <v>0.596566</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_3.txt</t>
+          <t>_2_3_3_1_1790732581_15.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.247814</v>
+        <v>0.246373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.542933</v>
+        <v>0.536555</v>
       </c>
       <c r="H5" t="n">
-        <v>0.513109</v>
+        <v>0.540574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5276</v>
+        <v>0.538557</v>
       </c>
       <c r="J5" t="n">
-        <v>0.251994</v>
+        <v>0.251124</v>
       </c>
       <c r="K5" t="n">
-        <v>0.566038</v>
+        <v>0.58371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.535714</v>
+        <v>0.575893</v>
       </c>
       <c r="M5" t="n">
-        <v>0.550459</v>
+        <v>0.579775</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_16.txt</t>
+          <t>_2_6_1_1790732533_11.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>6</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.246468</v>
+        <v>0.248467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.519608</v>
+        <v>0.51418</v>
       </c>
       <c r="H6" t="n">
-        <v>0.529338</v>
+        <v>0.520599</v>
       </c>
       <c r="I6" t="n">
-        <v>0.524428</v>
+        <v>0.51737</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25102</v>
+        <v>0.251172</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5642200000000001</v>
+        <v>0.538117</v>
       </c>
       <c r="L6" t="n">
-        <v>0.549107</v>
+        <v>0.535714</v>
       </c>
       <c r="M6" t="n">
-        <v>0.556561</v>
+        <v>0.536913</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_7.txt</t>
+          <t>_2_3_3_1_1790732581_14.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>6</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,7 +1086,7 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.241443</v>
+        <v>0.246468</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.560137</v>
+        <v>0.519608</v>
       </c>
       <c r="H7" t="n">
-        <v>0.610487</v>
+        <v>0.529338</v>
       </c>
       <c r="I7" t="n">
-        <v>0.584229</v>
+        <v>0.524428</v>
       </c>
       <c r="J7" t="n">
-        <v>0.25012</v>
+        <v>0.25102</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.5642200000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.589286</v>
+        <v>0.549107</v>
       </c>
       <c r="M7" t="n">
-        <v>0.594595</v>
+        <v>0.556561</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_1.txt</t>
+          <t>_2_6_1_1790732533_7.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1187,7 +1187,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.242029</v>
+        <v>0.246733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.571788</v>
+        <v>0.52327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.566792</v>
+        <v>0.519351</v>
       </c>
       <c r="I8" t="n">
-        <v>0.569279</v>
+        <v>0.521303</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251605</v>
+        <v>0.25149</v>
       </c>
       <c r="K8" t="n">
-        <v>0.57</v>
+        <v>0.563981</v>
       </c>
       <c r="L8" t="n">
-        <v>0.508929</v>
+        <v>0.53125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.537736</v>
+        <v>0.547126</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_14.txt</t>
+          <t>_2_6_1_1790732533_6.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.248118</v>
+        <v>0.247564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.506122</v>
+        <v>0.546997</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6192260000000001</v>
+        <v>0.523096</v>
       </c>
       <c r="I11" t="n">
-        <v>0.55699</v>
+        <v>0.53478</v>
       </c>
       <c r="J11" t="n">
-        <v>0.251212</v>
+        <v>0.252212</v>
       </c>
       <c r="K11" t="n">
-        <v>0.543307</v>
+        <v>0.568807</v>
       </c>
       <c r="L11" t="n">
-        <v>0.616071</v>
+        <v>0.553571</v>
       </c>
       <c r="M11" t="n">
-        <v>0.577406</v>
+        <v>0.561086</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_19.txt</t>
+          <t>_2_3_3_1_1790732581_6.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.24783</v>
+        <v>0.246663</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.539062</v>
+        <v>0.527027</v>
       </c>
       <c r="H12" t="n">
-        <v>0.516854</v>
+        <v>0.535581</v>
       </c>
       <c r="I12" t="n">
-        <v>0.527725</v>
+        <v>0.531269</v>
       </c>
       <c r="J12" t="n">
-        <v>0.251994</v>
+        <v>0.251026</v>
       </c>
       <c r="K12" t="n">
-        <v>0.570093</v>
+        <v>0.572727</v>
       </c>
       <c r="L12" t="n">
-        <v>0.544643</v>
+        <v>0.5625</v>
       </c>
       <c r="M12" t="n">
-        <v>0.557078</v>
+        <v>0.567568</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_4.txt</t>
+          <t>_2_6_1_1790732533_5.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.248509</v>
+        <v>0.24262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.527778</v>
+        <v>0.538732</v>
       </c>
       <c r="H13" t="n">
-        <v>0.569288</v>
+        <v>0.573034</v>
       </c>
       <c r="I13" t="n">
-        <v>0.547748</v>
+        <v>0.555354</v>
       </c>
       <c r="J13" t="n">
-        <v>0.250707</v>
+        <v>0.25187</v>
       </c>
       <c r="K13" t="n">
-        <v>0.556962</v>
+        <v>0.56682</v>
       </c>
       <c r="L13" t="n">
-        <v>0.589286</v>
+        <v>0.549107</v>
       </c>
       <c r="M13" t="n">
-        <v>0.572668</v>
+        <v>0.557823</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,23 +1763,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_2.txt</t>
+          <t>_2_6_1_1790732533_12.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>6</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1793,42 +1793,42 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.246459</v>
+        <v>0.248511</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.523114</v>
+        <v>0.5231789999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.536829</v>
+        <v>0.59176</v>
       </c>
       <c r="I14" t="n">
-        <v>0.529883</v>
+        <v>0.55536</v>
       </c>
       <c r="J14" t="n">
-        <v>0.251093</v>
+        <v>0.250715</v>
       </c>
       <c r="K14" t="n">
-        <v>0.561644</v>
+        <v>0.578947</v>
       </c>
       <c r="L14" t="n">
-        <v>0.549107</v>
+        <v>0.638393</v>
       </c>
       <c r="M14" t="n">
-        <v>0.555305</v>
+        <v>0.607219</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_0.txt</t>
+          <t>_2_3_3_1_1790732581_18.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>6</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.248511</v>
+        <v>0.248506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5231789999999999</v>
+        <v>0.523757</v>
       </c>
       <c r="H15" t="n">
         <v>0.59176</v>
       </c>
       <c r="I15" t="n">
-        <v>0.55536</v>
+        <v>0.555686</v>
       </c>
       <c r="J15" t="n">
-        <v>0.250715</v>
+        <v>0.250945</v>
       </c>
       <c r="K15" t="n">
-        <v>0.578947</v>
+        <v>0.5853660000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.638393</v>
+        <v>0.642857</v>
       </c>
       <c r="M15" t="n">
-        <v>0.607219</v>
+        <v>0.612766</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_18.txt</t>
+          <t>_2_3_3_1_1790732581_8.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.246733</v>
+        <v>0.246459</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52327</v>
+        <v>0.523114</v>
       </c>
       <c r="H16" t="n">
-        <v>0.519351</v>
+        <v>0.536829</v>
       </c>
       <c r="I16" t="n">
-        <v>0.521303</v>
+        <v>0.529883</v>
       </c>
       <c r="J16" t="n">
-        <v>0.25149</v>
+        <v>0.251093</v>
       </c>
       <c r="K16" t="n">
-        <v>0.563981</v>
+        <v>0.561644</v>
       </c>
       <c r="L16" t="n">
-        <v>0.53125</v>
+        <v>0.549107</v>
       </c>
       <c r="M16" t="n">
-        <v>0.547126</v>
+        <v>0.555305</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_6.txt</t>
+          <t>_2_6_1_1790732533_0.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.248484</v>
+        <v>0.248507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.518477</v>
+        <v>0.5278080000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.578027</v>
+        <v>0.604245</v>
       </c>
       <c r="I17" t="n">
-        <v>0.546635</v>
+        <v>0.563446</v>
       </c>
       <c r="J17" t="n">
-        <v>0.251087</v>
+        <v>0.251064</v>
       </c>
       <c r="K17" t="n">
-        <v>0.529412</v>
+        <v>0.570281</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5625</v>
+        <v>0.633929</v>
       </c>
       <c r="M17" t="n">
-        <v>0.545455</v>
+        <v>0.600423</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_1.txt</t>
+          <t>_2_3_3_1_1790732581_3.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.243157</v>
+        <v>0.244257</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5381899999999999</v>
+        <v>0.545692</v>
       </c>
       <c r="H18" t="n">
-        <v>0.571785</v>
+        <v>0.521848</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5544790000000001</v>
+        <v>0.5335029999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.252149</v>
+        <v>0.251998</v>
       </c>
       <c r="K18" t="n">
-        <v>0.571429</v>
+        <v>0.5792079999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.535714</v>
+        <v>0.522321</v>
       </c>
       <c r="M18" t="n">
-        <v>0.552995</v>
+        <v>0.549296</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_19.txt</t>
+          <t>_2_6_1_1790732533_3.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.248567</v>
+        <v>0.247814</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5223370000000001</v>
+        <v>0.542933</v>
       </c>
       <c r="H19" t="n">
-        <v>0.569288</v>
+        <v>0.513109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.544803</v>
+        <v>0.5276</v>
       </c>
       <c r="J19" t="n">
-        <v>0.250948</v>
+        <v>0.251994</v>
       </c>
       <c r="K19" t="n">
-        <v>0.57438</v>
+        <v>0.566038</v>
       </c>
       <c r="L19" t="n">
-        <v>0.620536</v>
+        <v>0.535714</v>
       </c>
       <c r="M19" t="n">
-        <v>0.596566</v>
+        <v>0.550459</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_15.txt</t>
+          <t>_2_3_3_1_1790732581_16.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.248269</v>
+        <v>0.24813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5334989999999999</v>
+        <v>0.512579</v>
       </c>
       <c r="H20" t="n">
-        <v>0.536829</v>
+        <v>0.610487</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5351590000000001</v>
+        <v>0.557265</v>
       </c>
       <c r="J20" t="n">
-        <v>0.25177</v>
+        <v>0.251147</v>
       </c>
       <c r="K20" t="n">
-        <v>0.537118</v>
+        <v>0.534413</v>
       </c>
       <c r="L20" t="n">
-        <v>0.549107</v>
+        <v>0.589286</v>
       </c>
       <c r="M20" t="n">
-        <v>0.543046</v>
+        <v>0.56051</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_11.txt</t>
+          <t>_2_3_3_1_1790732581_17.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,7 +2500,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.24262</v>
+        <v>0.241443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.538732</v>
+        <v>0.560137</v>
       </c>
       <c r="H21" t="n">
-        <v>0.573034</v>
+        <v>0.610487</v>
       </c>
       <c r="I21" t="n">
-        <v>0.555354</v>
+        <v>0.584229</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25187</v>
+        <v>0.25012</v>
       </c>
       <c r="K21" t="n">
-        <v>0.56682</v>
+        <v>0.6</v>
       </c>
       <c r="L21" t="n">
-        <v>0.549107</v>
+        <v>0.589286</v>
       </c>
       <c r="M21" t="n">
-        <v>0.557823</v>
+        <v>0.594595</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_12.txt</t>
+          <t>_2_6_1_1790732533_1.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.248194</v>
+        <v>0.248269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2618,25 +2618,25 @@
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.516741</v>
+        <v>0.5334989999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.578027</v>
+        <v>0.536829</v>
       </c>
       <c r="I22" t="n">
-        <v>0.545669</v>
+        <v>0.5351590000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.251287</v>
+        <v>0.25177</v>
       </c>
       <c r="K22" t="n">
-        <v>0.561983</v>
+        <v>0.537118</v>
       </c>
       <c r="L22" t="n">
-        <v>0.607143</v>
+        <v>0.549107</v>
       </c>
       <c r="M22" t="n">
-        <v>0.583691</v>
+        <v>0.543046</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_10.txt</t>
+          <t>_2_3_3_1_1790732581_11.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2702,7 +2702,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.244257</v>
+        <v>0.246438</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2719,25 +2719,25 @@
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.545692</v>
+        <v>0.551047</v>
       </c>
       <c r="H23" t="n">
-        <v>0.521848</v>
+        <v>0.525593</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5335029999999999</v>
+        <v>0.538019</v>
       </c>
       <c r="J23" t="n">
-        <v>0.251998</v>
+        <v>0.252281</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5792079999999999</v>
+        <v>0.567442</v>
       </c>
       <c r="L23" t="n">
-        <v>0.522321</v>
+        <v>0.544643</v>
       </c>
       <c r="M23" t="n">
-        <v>0.549296</v>
+        <v>0.555809</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_3.txt</t>
+          <t>_2_6_1_1790732533_13.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2803,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.248467</v>
+        <v>0.248509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.51418</v>
+        <v>0.527778</v>
       </c>
       <c r="H24" t="n">
-        <v>0.520599</v>
+        <v>0.569288</v>
       </c>
       <c r="I24" t="n">
-        <v>0.51737</v>
+        <v>0.547748</v>
       </c>
       <c r="J24" t="n">
-        <v>0.251172</v>
+        <v>0.250707</v>
       </c>
       <c r="K24" t="n">
-        <v>0.538117</v>
+        <v>0.556962</v>
       </c>
       <c r="L24" t="n">
-        <v>0.535714</v>
+        <v>0.589286</v>
       </c>
       <c r="M24" t="n">
-        <v>0.536913</v>
+        <v>0.572668</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_14.txt</t>
+          <t>_2_3_3_1_1790732581_2.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2904,7 +2904,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.244766</v>
+        <v>0.246525</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.540436</v>
+        <v>0.544767</v>
       </c>
       <c r="H25" t="n">
-        <v>0.525593</v>
+        <v>0.539326</v>
       </c>
       <c r="I25" t="n">
-        <v>0.532911</v>
+        <v>0.542033</v>
       </c>
       <c r="J25" t="n">
-        <v>0.251623</v>
+        <v>0.251308</v>
       </c>
       <c r="K25" t="n">
-        <v>0.591133</v>
+        <v>0.570093</v>
       </c>
       <c r="L25" t="n">
-        <v>0.535714</v>
+        <v>0.544643</v>
       </c>
       <c r="M25" t="n">
-        <v>0.562061</v>
+        <v>0.557078</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_17.txt</t>
+          <t>_2_6_1_1790732533_18.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.246663</v>
+        <v>0.24783</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.527027</v>
+        <v>0.539062</v>
       </c>
       <c r="H26" t="n">
-        <v>0.535581</v>
+        <v>0.516854</v>
       </c>
       <c r="I26" t="n">
-        <v>0.531269</v>
+        <v>0.527725</v>
       </c>
       <c r="J26" t="n">
-        <v>0.251026</v>
+        <v>0.251994</v>
       </c>
       <c r="K26" t="n">
-        <v>0.572727</v>
+        <v>0.570093</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5625</v>
+        <v>0.544643</v>
       </c>
       <c r="M26" t="n">
-        <v>0.567568</v>
+        <v>0.557078</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_5.txt</t>
+          <t>_2_3_3_1_1790732581_4.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>6</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.246353</v>
+        <v>0.242029</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.532178</v>
+        <v>0.571788</v>
       </c>
       <c r="H27" t="n">
-        <v>0.536829</v>
+        <v>0.566792</v>
       </c>
       <c r="I27" t="n">
-        <v>0.534493</v>
+        <v>0.569279</v>
       </c>
       <c r="J27" t="n">
-        <v>0.251143</v>
+        <v>0.251605</v>
       </c>
       <c r="K27" t="n">
-        <v>0.564815</v>
+        <v>0.57</v>
       </c>
       <c r="L27" t="n">
-        <v>0.544643</v>
+        <v>0.508929</v>
       </c>
       <c r="M27" t="n">
-        <v>0.554545</v>
+        <v>0.537736</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_8.txt</t>
+          <t>_2_6_1_1790732533_14.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.248326</v>
+        <v>0.248484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
+        <v>0.518477</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.578027</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.546635</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.251087</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.529412</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.573034</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.55036</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.251511</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.534979</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.580357</v>
+        <v>0.5625</v>
       </c>
       <c r="M28" t="n">
-        <v>0.556745</v>
+        <v>0.545455</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_12.txt</t>
+          <t>_2_3_3_1_1790732581_1.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.248545</v>
+        <v>0.248118</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.526667</v>
+        <v>0.506122</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59176</v>
+        <v>0.6192260000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.557319</v>
+        <v>0.55699</v>
       </c>
       <c r="J29" t="n">
-        <v>0.251014</v>
+        <v>0.251212</v>
       </c>
       <c r="K29" t="n">
-        <v>0.576613</v>
+        <v>0.543307</v>
       </c>
       <c r="L29" t="n">
-        <v>0.638393</v>
+        <v>0.616071</v>
       </c>
       <c r="M29" t="n">
-        <v>0.605932</v>
+        <v>0.577406</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_7.txt</t>
+          <t>_2_3_3_1_1790732581_19.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.246525</v>
+        <v>0.248106</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.544767</v>
+        <v>0.5272520000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.539326</v>
+        <v>0.59176</v>
       </c>
       <c r="I30" t="n">
-        <v>0.542033</v>
+        <v>0.557647</v>
       </c>
       <c r="J30" t="n">
-        <v>0.251308</v>
+        <v>0.251351</v>
       </c>
       <c r="K30" t="n">
-        <v>0.570093</v>
+        <v>0.596774</v>
       </c>
       <c r="L30" t="n">
-        <v>0.544643</v>
+        <v>0.660714</v>
       </c>
       <c r="M30" t="n">
-        <v>0.557078</v>
+        <v>0.627119</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_18.txt</t>
+          <t>_2_3_3_1_1790732581_9.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>6</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.243936</v>
+        <v>0.248326</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.546697</v>
+        <v>0.529412</v>
       </c>
       <c r="H31" t="n">
-        <v>0.599251</v>
+        <v>0.573034</v>
       </c>
       <c r="I31" t="n">
-        <v>0.571769</v>
+        <v>0.55036</v>
       </c>
       <c r="J31" t="n">
-        <v>0.251316</v>
+        <v>0.251511</v>
       </c>
       <c r="K31" t="n">
-        <v>0.573394</v>
+        <v>0.534979</v>
       </c>
       <c r="L31" t="n">
-        <v>0.558036</v>
+        <v>0.580357</v>
       </c>
       <c r="M31" t="n">
-        <v>0.565611</v>
+        <v>0.556745</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_16.txt</t>
+          <t>_2_3_3_1_1790732581_12.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>6</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3611,7 +3611,7 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.24573</v>
+        <v>0.246247</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.543791</v>
+        <v>0.528822</v>
       </c>
       <c r="H32" t="n">
-        <v>0.519351</v>
+        <v>0.526841</v>
       </c>
       <c r="I32" t="n">
-        <v>0.53129</v>
+        <v>0.52783</v>
       </c>
       <c r="J32" t="n">
-        <v>0.252592</v>
+        <v>0.251108</v>
       </c>
       <c r="K32" t="n">
-        <v>0.574879</v>
+        <v>0.574661</v>
       </c>
       <c r="L32" t="n">
-        <v>0.53125</v>
+        <v>0.566964</v>
       </c>
       <c r="M32" t="n">
-        <v>0.552204</v>
+        <v>0.570787</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_4.txt</t>
+          <t>_2_6_1_1790732533_10.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3712,42 +3712,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.24813</v>
+        <v>0.246353</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E33" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.512579</v>
+        <v>0.532178</v>
       </c>
       <c r="H33" t="n">
-        <v>0.610487</v>
+        <v>0.536829</v>
       </c>
       <c r="I33" t="n">
-        <v>0.557265</v>
+        <v>0.534493</v>
       </c>
       <c r="J33" t="n">
-        <v>0.251147</v>
+        <v>0.251143</v>
       </c>
       <c r="K33" t="n">
-        <v>0.534413</v>
+        <v>0.564815</v>
       </c>
       <c r="L33" t="n">
-        <v>0.589286</v>
+        <v>0.544643</v>
       </c>
       <c r="M33" t="n">
-        <v>0.56051</v>
+        <v>0.554545</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,23 +3783,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_17.txt</t>
+          <t>_2_6_1_1790732533_8.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>6</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.247564</v>
+        <v>0.248478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.546997</v>
+        <v>0.522532</v>
       </c>
       <c r="H35" t="n">
-        <v>0.523096</v>
+        <v>0.60799</v>
       </c>
       <c r="I35" t="n">
-        <v>0.53478</v>
+        <v>0.5620309999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.252212</v>
+        <v>0.250792</v>
       </c>
       <c r="K35" t="n">
-        <v>0.568807</v>
+        <v>0.574219</v>
       </c>
       <c r="L35" t="n">
-        <v>0.553571</v>
+        <v>0.65625</v>
       </c>
       <c r="M35" t="n">
-        <v>0.561086</v>
+        <v>0.6125</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_6.txt</t>
+          <t>_2_3_3_1_1790732581_13.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.248106</v>
+        <v>0.248194</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5272520000000001</v>
+        <v>0.516741</v>
       </c>
       <c r="H36" t="n">
-        <v>0.59176</v>
+        <v>0.578027</v>
       </c>
       <c r="I36" t="n">
-        <v>0.557647</v>
+        <v>0.545669</v>
       </c>
       <c r="J36" t="n">
-        <v>0.251351</v>
+        <v>0.251287</v>
       </c>
       <c r="K36" t="n">
-        <v>0.596774</v>
+        <v>0.561983</v>
       </c>
       <c r="L36" t="n">
-        <v>0.660714</v>
+        <v>0.607143</v>
       </c>
       <c r="M36" t="n">
-        <v>0.627119</v>
+        <v>0.583691</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_9.txt</t>
+          <t>_2_3_3_1_1790732581_10.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4116,7 +4116,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.245596</v>
+        <v>0.243936</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.531131</v>
+        <v>0.546697</v>
       </c>
       <c r="H37" t="n">
-        <v>0.521848</v>
+        <v>0.599251</v>
       </c>
       <c r="I37" t="n">
-        <v>0.526448</v>
+        <v>0.571769</v>
       </c>
       <c r="J37" t="n">
-        <v>0.25158</v>
+        <v>0.251316</v>
       </c>
       <c r="K37" t="n">
-        <v>0.578199</v>
+        <v>0.573394</v>
       </c>
       <c r="L37" t="n">
-        <v>0.544643</v>
+        <v>0.558036</v>
       </c>
       <c r="M37" t="n">
-        <v>0.56092</v>
+        <v>0.565611</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_2.txt</t>
+          <t>_2_6_1_1790732533_16.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.246247</v>
+        <v>0.24573</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4234,25 +4234,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.528822</v>
+        <v>0.543791</v>
       </c>
       <c r="H38" t="n">
-        <v>0.526841</v>
+        <v>0.519351</v>
       </c>
       <c r="I38" t="n">
-        <v>0.52783</v>
+        <v>0.53129</v>
       </c>
       <c r="J38" t="n">
-        <v>0.251108</v>
+        <v>0.252592</v>
       </c>
       <c r="K38" t="n">
-        <v>0.574661</v>
+        <v>0.574879</v>
       </c>
       <c r="L38" t="n">
-        <v>0.566964</v>
+        <v>0.53125</v>
       </c>
       <c r="M38" t="n">
-        <v>0.570787</v>
+        <v>0.552204</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_10.txt</t>
+          <t>_2_6_1_1790732533_4.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.246373</v>
+        <v>0.247229</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790732533</v>
+        <v>1790732581</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.536555</v>
+        <v>0.540173</v>
       </c>
       <c r="H39" t="n">
-        <v>0.540574</v>
+        <v>0.5455680000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0.538557</v>
+        <v>0.542857</v>
       </c>
       <c r="J39" t="n">
-        <v>0.251124</v>
+        <v>0.252492</v>
       </c>
       <c r="K39" t="n">
-        <v>0.58371</v>
+        <v>0.568807</v>
       </c>
       <c r="L39" t="n">
-        <v>0.575893</v>
+        <v>0.553571</v>
       </c>
       <c r="M39" t="n">
-        <v>0.579775</v>
+        <v>0.561086</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_6_1_1790732533_11.txt</t>
+          <t>_2_3_3_1_1790732581_5.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>6</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,42 +4419,42 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.247229</v>
+        <v>0.245596</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E40" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F40" t="n">
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.540173</v>
+        <v>0.531131</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5455680000000001</v>
+        <v>0.521848</v>
       </c>
       <c r="I40" t="n">
-        <v>0.542857</v>
+        <v>0.526448</v>
       </c>
       <c r="J40" t="n">
-        <v>0.252492</v>
+        <v>0.25158</v>
       </c>
       <c r="K40" t="n">
-        <v>0.568807</v>
+        <v>0.578199</v>
       </c>
       <c r="L40" t="n">
-        <v>0.553571</v>
+        <v>0.544643</v>
       </c>
       <c r="M40" t="n">
-        <v>0.561086</v>
+        <v>0.56092</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,23 +4490,23 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_5.txt</t>
+          <t>_2_6_1_1790732533_2.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z40" t="n">
         <v>6</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.248506</v>
+        <v>0.244766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790732581</v>
+        <v>1790732533</v>
       </c>
       <c r="E41" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.523757</v>
+        <v>0.540436</v>
       </c>
       <c r="H41" t="n">
-        <v>0.59176</v>
+        <v>0.525593</v>
       </c>
       <c r="I41" t="n">
-        <v>0.555686</v>
+        <v>0.532911</v>
       </c>
       <c r="J41" t="n">
-        <v>0.250945</v>
+        <v>0.251623</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5853660000000001</v>
+        <v>0.591133</v>
       </c>
       <c r="L41" t="n">
-        <v>0.642857</v>
+        <v>0.535714</v>
       </c>
       <c r="M41" t="n">
-        <v>0.612766</v>
+        <v>0.562061</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790732581_8.txt</t>
+          <t>_2_6_1_1790732533_17.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.5764334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02726507309708657</v>
+        <v>0.02726507309708658</v>
       </c>
       <c r="D2" t="n">
         <v>0.627119</v>
@@ -4710,7 +4710,7 @@
         <v>0.5600418</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01317729917060318</v>
+        <v>0.01317729917060317</v>
       </c>
       <c r="D3" t="n">
         <v>0.594595</v>
